--- a/sales_order_forms/011_process_control_unit_order_form--sales_order_forms.xlsx
+++ b/sales_order_forms/011_process_control_unit_order_form--sales_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'online_payment'}</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Online Payment'}</t>
+          <t>Online Payment</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'offline_payment'}</t>
+          <t>offline_payment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Offline Payment'}</t>
+          <t>Offline Payment</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'unit_1'}</t>
+          <t>unit_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Unit 1'}</t>
+          <t>Unit 1</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'unit_2'}</t>
+          <t>unit_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Unit 2'}</t>
+          <t>Unit 2</t>
         </is>
       </c>
     </row>
